--- a/dcf/ISRG.xlsx
+++ b/dcf/ISRG.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>203.3437860456147</v>
+        <v>186.1417202550087</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>196.5101913011373</v>
+        <v>180.0142890757934</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>189.9824080260457</v>
+        <v>174.1597745684352</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>183.7449728017121</v>
+        <v>168.564405096794</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>177.7832802023162</v>
+        <v>163.2151723338123</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>172.0835312881264</v>
+        <v>158.0997854670423</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>166.632685414833</v>
+        <v>153.2066283513292</v>
       </c>
     </row>
     <row r="6">
@@ -1171,25 +1171,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>215.3660149159021</v>
+        <v>196.8145973039553</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>207.9974296822723</v>
+        <v>190.2122219380434</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>200.9607273627551</v>
+        <v>183.905908479956</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>194.2390646419915</v>
+        <v>177.8806602737742</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>187.8165349695627</v>
+        <v>172.1223139035618</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>181.6781122318597</v>
+        <v>166.6174891186267</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>175.8095980548079</v>
+        <v>161.3535419854093</v>
       </c>
     </row>
     <row r="7">
@@ -1197,25 +1197,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>227.3882437861896</v>
+        <v>207.4874743529019</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>219.4846680634074</v>
+        <v>200.4101548002934</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>211.9390466994646</v>
+        <v>193.6520423914768</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>204.733156482271</v>
+        <v>187.1969154507544</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>197.8497897368092</v>
+        <v>181.0294554733112</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>191.2726931755929</v>
+        <v>175.1351927702111</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>184.9865106947827</v>
+        <v>169.5004556194893</v>
       </c>
     </row>
     <row r="8">
@@ -1223,25 +1223,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>239.4104726564771</v>
+        <v>218.1603514018486</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>230.9719064445424</v>
+        <v>210.6080876625433</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>222.917366036174</v>
+        <v>203.3981763029976</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>215.2272483225504</v>
+        <v>196.5131706277346</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>207.8830445040557</v>
+        <v>189.9365970430606</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>200.8672741193261</v>
+        <v>183.6528964217954</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>194.1634233347576</v>
+        <v>177.6473692535694</v>
       </c>
     </row>
     <row r="9">
@@ -1249,25 +1249,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>251.4327015267646</v>
+        <v>228.8332284507952</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>242.4591448256774</v>
+        <v>220.8060205247933</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>233.8956853728835</v>
+        <v>213.1443102145184</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>225.7213401628298</v>
+        <v>205.8294258047148</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>217.9162992713022</v>
+        <v>198.8437386128101</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>210.4618550630593</v>
+        <v>192.1706000733798</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>203.3403359747325</v>
+        <v>185.7942828876494</v>
       </c>
     </row>
     <row r="10">
@@ -1275,25 +1275,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>263.4549303970521</v>
+        <v>239.5061054997418</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>253.9463832068125</v>
+        <v>231.0039533870433</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>244.8740047095929</v>
+        <v>222.8904441260392</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>236.2154320031092</v>
+        <v>215.145680981695</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>227.9495540385487</v>
+        <v>207.7508801825595</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>220.0564360067925</v>
+        <v>200.6883037249642</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>212.5172486147073</v>
+        <v>193.9411965217295</v>
       </c>
     </row>
     <row r="11">
@@ -1301,25 +1301,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>275.4771592673396</v>
+        <v>250.1789825486885</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>265.4336215879475</v>
+        <v>241.2018862492932</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>255.8523240463024</v>
+        <v>232.63657803756</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>246.7095238433887</v>
+        <v>224.4619361586752</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>237.9828088057951</v>
+        <v>216.6580217523089</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>229.6510169505258</v>
+        <v>209.2060073765486</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>221.6941612546822</v>
+        <v>202.0881101558095</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>426.010009765625</v>
+        <v>426.6098937988281</v>
       </c>
     </row>
     <row r="14">
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9628096671649029</v>
+        <v>0.9664270987534533</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24456,7 +24456,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>426.010009765625</v>
+        <v>426.6098937988281</v>
       </c>
     </row>
     <row r="49">
@@ -24466,7 +24466,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24618,13 +24618,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>215.2272483225504</v>
+        <v>196.5131706277346</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>286.544468677438</v>
+        <v>255.2161692247756</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>161.1463059551949</v>
+        <v>150.7556662816507</v>
       </c>
     </row>
     <row r="59">
